--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -113,7 +113,7 @@
     <t>MESObservationGlucose</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS|1.2.0 (extensible)</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS|20250728120000 (extensible)</t>
   </si>
   <si>
     <t>MESObservationHeadCircumference</t>
